--- a/Machine Learning/PII/Interim-report/Papers/Papers-Table.xlsx
+++ b/Machine Learning/PII/Interim-report/Papers/Papers-Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\git\Machine Learning\PII\Interim-report\Papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A69A2C5-E8CE-4B4E-8F75-93F137AF8224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00020E7-CFA5-4F98-92CD-5451111677E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA821531-E608-40CF-B71D-4D7770E4DFA0}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="LLM Questions" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="204">
   <si>
     <t>Bae, Y., Kim, M., Lee, J., Kim, S., Kim, J., Choi, Y., &amp; Mireshghallah, N. (2025). Privacy-Preserving LLM Interaction with Socratic Chain-of-Thought Reasoning and Homomorphically Encrypted Vector Databases.</t>
   </si>
@@ -3539,6 +3540,555 @@
   <si>
     <t>The paper highlights that its findings primarily apply to kNN-LMs, with further study needed to understand privacy implications for other retrieval-based models like RETRO or Atlas. The specific choices of public datasets may also limit the generalizability of the findings.
 For future work, the authors suggest investigating other retrieval-based LM architectures and exploring alternative public datasets. They also emphasize combining proposed mitigation strategies with more diverse privacy-preserving techniques, particularly for the challenging problem of untargeted privacy risks</t>
+  </si>
+  <si>
+    <t>Preventing Generation of Verbatim Memorization in Language Models Gives a False Sense of Privacy - ACL Anthology</t>
+  </si>
+  <si>
+    <t>Preventing Generation of Verbatim Memorization in Language Models Gives a False Sense of Privacy</t>
+  </si>
+  <si>
+    <r>
+      <t>This research investigates how </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>language models memorize training data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, arguing that current definitions of memorization are too narrow. The authors introduce "MEMFREE decoding," a defense mechanism designed to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>prevent exact, "verbatim memorization"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> by filtering out n-grams that precisely match training data. However, they demonstrate that this perfect filter can be </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>easily bypassed through "style-transfer" prompts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, which minimally alter the input to elicit memorized content that is not an exact match. The paper concludes by advocating for a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>broader definition of memorization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> that encompasses approximate or semantically similar outputs, highlighting the need for more robust privacy defenses in large language models like GitHub's Copilot.</t>
+    </r>
+  </si>
+  <si>
+    <t>The main focus of this paper is to challenge the adequacy of "verbatim memorization" definitions in neural language models and demonstrate that preventing it gives a false sense of privacy. The authors argue that current definitions, which focus on exact matches to training data, are too restrictive and fail to capture more subtle forms of memorization.
+Through the development of an efficient defense called MEMFREE decoding, which perfectly prevents all verbatim memorization, the paper shows that training data can still be leaked. This leakage occurs through "style-transfer" prompts and approximate memorization, where models generate content that is semantically similar but not an exact copy of the training data. The work concludes that a broader definition of memorization, incorporating semantic similarity, is crucial for understanding and mitigating privacy risks in language models</t>
+  </si>
+  <si>
+    <t>The main focus of this paper is to challenge the adequacy of "verbatim memorization" definitions in neural language models and demonstrate that preventing it gives a false sense of privacy. The authors argue that current definitions, which focus on exact matches to training data, are too restrictive and fail to capture more subtle forms of memorization.
+Through the development of an efficient defense called MEMFREE decoding, which perfectly prevents all verbatim memorization, the paper shows that training data can still be leaked. This leakage occurs through "style-transfer" prompts and approximate memorization, where models generate content that is semantically similar but not an exact copy of the training data. The work concludes that a broader definition of memorization, incorporating semantic similarity, is crucial for understanding and mitigating privacy risks in language models.
+Explain me the methodology used in less than 150 words?
+The methodology employed in this paper revolves around two key aspects: developing a defense against verbatim memorization and then demonstrating its insufficiency. The authors developed MEMFREE decoding, an efficient, inference-time defense guaranteed to perfectly prevent all verbatim memorization. This works by checking each generated n-gram against a Bloom filter of common training set n-grams and re-sampling tokens if a match is found, thus avoiding exact copies.
+To challenge the adequacy of verbatim definitions, the paper uses this perfect filter and also conducts experiments with other models like GitHub Copilot, GPT-3, and PaLM. They demonstrate that "style-transfer" prompts (e.g., changing variable names, capitalization, or adding comments) easily circumvent verbatim filters, leading to the leakage of training data through "approximate memorization". This approximate memorization is quantified using metrics like BLEU score and Levenshtein similarity, with a BLEU score of 0.75 or higher indicating substantial memorization</t>
+  </si>
+  <si>
+    <t>The paper demonstrates that preventing verbatim memorization in neural language models gives a false sense of privacy. Even with a perfect verbatim filter like MEMFREE decoding, training data can still be leaked through "style-transfer" prompts and approximate memorization. Models such as GitHub Copilot, GPT-3, and PaLM were shown to bypass these filters by generating content that is semantically similar but not an exact copy of the training data. This highlights the necessity for a broader definition of memorization that includes semantic similarity</t>
+  </si>
+  <si>
+    <t>The paper highlights that verbatim memorization definitions are too restrictive and easily circumvented by "style-transfer" prompts and approximate memorization, giving a false sense of privacy. A current shortcoming is that the proposed approximate memorization definition (BLEU &gt; 0.75) may be inaccurate, potentially over or under-counting, and could introduce false positives.
+Future work needs to focus on developing a broader definition of memorization that includes semantic similarity. This also involves exploring techniques from plagiarism detection to better define and minimize memorized data in LLMs and studying the interplay between memorization and general knowledge</t>
+  </si>
+  <si>
+    <t>[2302.00539] Analyzing Leakage of Personally Identifiable Information in Language Models</t>
+  </si>
+  <si>
+    <t>Analyzing Leakage of Personally Identifiable Information in Language Models</t>
+  </si>
+  <si>
+    <r>
+      <t>This research investigates the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>vulnerability of Language Models (LMs) to leaking Personally Identifiable Information (PII)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, despite current data protection efforts. The authors introduce novel, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>game-based attack definitions for PII extraction, reconstruction, and inference</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> to rigorously assess these risks. They demonstrate that while existing defenses like PII scrubbing and differential privacy reduce leakage, they do not entirely eliminate it, with some PII still being extractable or inferable, particularly in larger models and with duplicated data. The study underscores the critical need for improved and more integrated privacy measures that balance utility and protection against sophisticated PII leakage attacks.</t>
+    </r>
+  </si>
+  <si>
+    <t>Table --&gt; Appoarch Description Advantages, Limitations</t>
+  </si>
+  <si>
+    <t>Para --&gt; Problem solution results Critical Analysis</t>
+  </si>
+  <si>
+    <t>This paper focuses on addressing information leakage in Federated Learning (FL). It proposes a novel framework called noising before model aggregation FL (NbAFL), where each client perturbs its trained parameters locally by adding noise before uploading them to a central server for aggregation.
+The main focus includes:
+• Providing a theoretical analysis of the convergence properties of differentially private FL algorithms, which was previously lacking in existing studies.
+• Proving that the NbAFL scheme satisfies differential privacy (DP) requirements under a certain noise perturbation level with Gaussian noise.
+• Developing a convergence bound on the loss function, revealing key trade-offs between convergence performance and privacy protection levels, the impact of the number of clients (N), and an optimal number of maximum aggregation times (T).
+• Analyzing the relationship between privacy levels, convergence performance, the number of clients, and global aggregations.
+• Defining a global (ε, δ)-DP requirement for both uplink and downlink channels and developing variances for artificial noise at clients and the server.
+Essentially, the paper provides analytical results to help design privacy-preserving FL architectures with specific trade-off requirements for performance and privacy</t>
+  </si>
+  <si>
+    <t>he methodology of this paper centers on noising before model aggregation Federated Learning (NbAFL), where clients locally perturb parameters with noise before uploading them.
+It involves:
+• Theoretical analysis: Developing a convergence bound on the loss function, revealing trade-offs between convergence performance and privacy protection, and the impact of client numbers (N) and aggregation times (T).
+• Differential Privacy (DP) proof: Proving that NbAFL satisfies DP under specific Gaussian noise perturbation levels by adapting their variances.
+• K-client random scheduling: Proposing and analyzing a strategy where a subset (K) of N clients participate in each aggregation, and developing a corresponding convergence bound.
+• Empirical validation: Conducting extensive simulations using multi-layer perceptron (MLP) and real-world federated datasets, varying protection levels (ε), N, T, and K to validate theoretical properties.
+The analytical and simulation results aim to facilitate the design of privacy-preserving FL architectures</t>
+  </si>
+  <si>
+    <t>The paper achieved several key outcomes for Federated Learning with differential privacy (DP). It proved that the proposed NbAFL scheme satisfies DP under specific Gaussian noise perturbation levels. A convergence bound was developed on the loss function, revealing an inherent trade-off between convergence performance and privacy protection levels.
+The study also identified an optimal number of aggregation times (T) and an optimal number of participating clients (K) to achieve the best convergence performance for a given privacy level. Extensive simulations consistently validated these theoretical results, thereby facilitating the design of privacy-preserving FL architectures</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> key shortcoming implicitly identified is the lack of analytical evaluation for NbAFL's convergence performance with varying sizes and distributions of data at client sides.
+As for future work, the paper suggests extending its research to analytically evaluate this very aspect: the convergence performance of NbAFL when client data varies in size and distribution. This aims to provide more comprehensive insights for designing privacy-preserving Federated Learning architectures</t>
+  </si>
+  <si>
+    <t>[2107.01614] Survey: Leakage and Privacy at Inference Time</t>
+  </si>
+  <si>
+    <t>Survey: Leakage and Privacy at Inference Time</t>
+  </si>
+  <si>
+    <r>
+      <t>This research paper offers a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>comprehensive survey of data leakage and privacy concerns in Machine Learning (ML) models during inference time</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, which is when publicly available models are used. It categorizes leakage into </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>involuntary data leakage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, which includes phenomena like overfitting and memorization, and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>malicious leakage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, stemming from privacy attacks. The paper details various privacy attacks, such as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Membership Inference Attacks (MIAs)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, where an adversary tries to determine if a specific data point was used in training, and </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Model Extraction Attacks (MEAs)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, aimed at stealing the model's functionality or parameters. Finally, it outlines current defense mechanisms, ranging from data-level techniques like obfuscation and sanitization to model-level strategies such as machine unlearning, knowledge distillation, and the application of differential privacy, while also addressing their limitations and challenges.</t>
+    </r>
+  </si>
+  <si>
+    <t>This paper presents a comprehensive survey of data leakage in trained Machine Learning (ML) models, with a primary focus on inference-time leakage from publicly available models. It provides a unified perspective on data leakage, categorizing it into involuntary leakage and malicious leakage (privacy attacks).
+The survey delves into existing defence mechanisms, assessment metrics, and applications for safeguarding sensitive data. Furthermore, it identifies outstanding challenges and open questions, outlining promising directions for future research in understanding and preventing data leakage in ML</t>
+  </si>
+  <si>
+    <t>This paper employs a comprehensive survey methodology to provide a unified perspective on data leakage in trained Machine Learning (ML) models. Its primary focus is on inference-time leakage from publicly available models.
+The methodology involves:
+• Categorization: Proposing a taxonomy that distinguishes between involuntary leakage (e.g., overfitting, memorization) and malicious leakage (privacy attacks like membership inference, model extraction, property inference, and reconstruction attacks).
+• Review of existing solutions: Describing currently available defence mechanisms (e.g., data obfuscation, sanitization, differential privacy), assessment metrics (e.g., re-identification score, privacy risk score), and applications (e.g., Data as a Service, MLaaS).
+• Identification of gaps: Concluding by outlining outstanding challenges and open questions for future research in the field.
+• Contextual analysis: Discussing leakage in the context of different data types and ML tasks.</t>
+  </si>
+  <si>
+    <t>This paper provides a comprehensive survey and unified perspective on data leakage in trained ML models, specifically focusing on inference-time leakage from publicly available models. It successfully categorizes leakage into involuntary and malicious types, and reviews existing defence mechanisms, assessment metrics, and applications. A key outcome is the identification of outstanding challenges and open questions, thereby outlining promising future research directions in understanding and preventing data leakage in Machine Learning</t>
+  </si>
+  <si>
+    <t>The paper highlights several shortcomings, including the uneven exploration of attacks and defenses across various data types and ML tasks. It notes the lack of computationally efficient and universally applicable defenses, with many being case-specific or failing to scale. Challenges also exist in verifying forgetting and in the elusiveness of synthetic data generation with convincing privacy guarantees.
+For future work, the paper calls for advancing attacks to uniformly probe weaknesses across different contexts and developing more general, efficient, and robust defense mechanisms. A crucial area is creating standardized detection and reporting frameworks and developing practical software to bridge the gap between theoretical research and real-world utility</t>
+  </si>
+  <si>
+    <t>Deidentification of free-text medical records using pre-trained bidirectional transformers - PubMed</t>
+  </si>
+  <si>
+    <t>Deidentification of free-text medical records using pre-trained bidirectional transformers</t>
+  </si>
+  <si>
+    <r>
+      <t>This paper introduces a novel approach to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>deidentifying free-text medical records</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> by leveraging pre-trained bidirectional transformer models, specifically BERT. The core challenge addressed is the critical need to </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>protect patient privacy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> when sharing medical data for research and clinical practice, as current deidentification methods often fall short, leading to either data being withheld or sensitive information being inadvertently disclosed. The authors detail their model's architecture, its evaluation against existing benchmarks, and the difficulties encountered, such as the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>scarcity of high-quality annotated data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> and the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>heterogeneity of identifiers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Ultimately, the research aims to provide a more effective and accessible tool for removing protected health information (PHI) from clinical notes, facilitating broader data sharing while adhering to privacy regulations like HIPAA.</t>
+    </r>
+  </si>
+  <si>
+    <t>This paper's main focus is on deidentification of free-text medical records to protect patient privacy during data sharing for clinical practice and biomedical research. It specifically develops and evaluates an approach for deidentification of clinical notes based on a bidirectional transformer model, BERT.
+The paper aims to achieve state-of-the-art performance in removing protected health information (PHI) like names, contact details, and dates from electronic health records. Key aspects of its focus include proposing human-interpretable evaluation measures, demonstrating superior performance compared to existing models, and addressing challenges such as inconsistent annotation guidelines, limited model portability, and scarcity of training data</t>
+  </si>
+  <si>
+    <t>The methodology employed in this paper involves developing and evaluating an approach for deidentification of free-text medical records using a bidirectional transformer model, BERT. The model architecture consists of L identical transformer layers, with their outputs fed into a linear, fully connected layer for named entity recognition (NER) across eight possible classes (seven PHI categories plus "other").
+Four publicly available clinical datasets (i2b2 2006, i2b2 2014, PhysioNet, Dernoncourt-Lee) were used, undergoing harmonization, tokenization (whitespace and WordPiece), and segment sampling. Models were initialized with pre-trained weights (BERT, SciBERT, or BioBERT) and fine-tuned using the Adam optimizer. Performance evaluation focused on positive predictive value (PPV), sensitivity (Se), and F1-measure, with a strong emphasis on sensitivity, and also reported false positives and false negatives per 1000 tokens for human interpretability</t>
+  </si>
+  <si>
+    <t>This paper achieved state-of-the-art performance in deidentification of free-text medical records using a BERT-based model, outperforming previous methods. It successfully removed protected health information (PHI) like names, ages, and dates.
+The study also introduced human-interpretable evaluation measures for model performance. It demonstrated that larger, case-insensitive models generally performed best. Critically, the work highlighted the trade-off between high sensitivity (minimal missed PHI) and an increased rate of false positives (over-redaction). The code for the model was made open source, enabling broad reuse</t>
+  </si>
+  <si>
+    <t>The paper identifies several shortcomings, including the scarcity of high-quality annotated data, lack of clear annotation guidelines, and limited model portability. It highlights significant challenges due to annotation ambiguities in defining Protected Health Information (PHI), which impedes cross-dataset comparisons and model generalization. BERT models also struggle with numeracy, and valuable document structure information is lost during tokenization.
+For future work, the paper suggests combining neural networks with rule-based approaches and exploring newer transformer models for enhanced performance. Crucially, it advocates for a community-wide consensus on PHI annotation protocols and clearer definitions to standardize the deidentification task and its evaluation</t>
+  </si>
+  <si>
+    <t>Differentially Private Fine-tuning of Language Models</t>
+  </si>
+  <si>
+    <r>
+      <t>This paper introduces an </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>adaptive framework for mitigating Personally Identifiable Information (PII) and Sensitive Personal Information (SPI) risks in Large Language Models (LLMs)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. The core challenge addressed is the increasing complexity of global data protection laws, such as GDPR and CCPA, which require LLMs to handle personal data with varying levels of strictness. The proposed system leverages </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>advanced NLP techniques, real-time contextual analysis, and policy-driven masking</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> to dynamically ensure compliance across diverse regulatory landscapes and seamlessly integrates with enterprise Governance, Risk, and Compliance (GRC) systems. Benchmarking results highlight the system's superior effectiveness compared to existing tools, achieving high accuracy in identifying and anonymizing sensitive data, ultimately fostering greater user trust in LLM deployments.</t>
+    </r>
+  </si>
+  <si>
+    <t>This paper's main focus is on mitigating the risk of Personally Identifiable Information (PII) and Sensitive Personal Information (SPI) leakage in Large Language Models (LLMs). It addresses the growing challenges posed by evolving global data protection regulations such as GDPR, CCPA, and PIPEDA, which complicate the training and deployment of LLMs that rely on extensive datasets.
+The paper introduces an adaptive framework designed to dynamically assess and mitigate these risks. This system leverages advanced Natural Language Processing (NLP) techniques, real-time contextual analysis, and policy-driven masking to ensure regulatory compliance across diverse frameworks and seamlessly integrates into enterprise Governance, Risk, and Compliance (GRC) systems. The aim is to provide a scalable and robust solution for ethical and compliant LLM deployment, particularly in critical sectors like healthcare and finance.</t>
+  </si>
+  <si>
+    <t>The methodology introduces an adaptive framework designed to dynamically assess and mitigate Personally Identifiable Information (PII) and Sensitive Personal Information (SPI) risks in Large Language Models (LLMs).
+This system consists of three key components:
+1. Adaptive Policy Engine: Converts global privacy regulations (like GDPR, CCPA, PIPEDA) into actionable, machine-readable rules, dynamically updated with domain expert input.
+2. Dynamic Contextual PII Detection: Employs Machine Learning models for entity recognition and performs semantic and proximity analysis. It identifies sensitive data by interpreting context and classifying entities into sensitivity levels.
+3. Adaptive Masking and Anonymization Techniques: Applies tailored remediation strategies, such as pseudonymization for names, hashing for IDs, and obfuscation for dates, based on PII sensitivity and specific regulatory requirements.
+The framework integrates seamlessly with enterprise Governance, Risk, and Compliance (GRC) systems. Its effectiveness is validated through benchmarks against state-of-the-art tools and human evaluations to confirm regulatory compliance and user trust</t>
+  </si>
+  <si>
+    <t>This paper achieved significant outcomes by introducing an adaptive framework for mitigating PII and SPI risks in Large Language Models (LLMs). It demonstrated an F1 score of 0.95 for Passport Numbers, outperforming state-of-the-art tools like Microsoft Presidio (0.33) and Amazon Comprehend (0.54).
+In human evaluations, the system attained an average user trust score of 4.6/5, with participants praising its accuracy and transparency. It successfully showed stricter anonymization under GDPR compared to CCPA, validating it as a scalable and robust solution for enterprise privacy compliance</t>
+  </si>
+  <si>
+    <t>The paper identifies several shortcomings, including the continuous evolution of data protection laws, the complexity of integrating conflicting jurisdictional requirements, and challenges in accurately identifying PII and SPI across languages and cultural contexts. Handling ambiguous data, such as distinguishing public figures' names from sensitive personal references, also requires improved edge case handling.
+For future work, the authors plan to refine compliance mechanisms to reconcile overlapping regulations (e.g., GDPR vs. CCPA) and expand the framework into additional domains like telecommunications and retail. Efforts are also underway to automate the integration of new regulations into the policy engine and improve efficiency for high-volume, real-time LLM interactions</t>
+  </si>
+  <si>
+    <t>(PDF) Navigating Data Protection Challenges in the Era of Artificial Intelligence: A Comprehensive Review</t>
+  </si>
+  <si>
+    <t>Navigating Data Protection Challenges in the Era of Artificial 
+Intelligence: A Comprehensive Review</t>
+  </si>
+  <si>
+    <r>
+      <t>This comprehensive review, "Navigating Data Protection Challenges in the Era of Artificial Intelligence," published in the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Revista de Inteligencia Artificial en Medicina</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> (2024), delves into the complex relationship between rapidly advancing AI technologies and the critical need for robust data protection. The authors, Anil Kumar Yadav Yanamala and Srikanth Suryadevara, both affiliated with South Carolina state departments, examine </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>regulatory frameworks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> like the GDPR and CCPA, highlighting their impact on data governance. Furthermore, the review addresses crucial </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ethical considerations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> surrounding AI, such as bias in decision-making, and explores </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>technological innovations</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF47484C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> like federated learning and differential privacy as promising solutions for preserving privacy in AI applications. Ultimately, the paper aims to synthesize current knowledge to provide valuable insights for policymakers, practitioners, and researchers navigating this evolving landscape.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3595,12 +4145,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF47484C"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="8"/>
       <color rgb="FF131314"/>
@@ -3609,6 +4153,12 @@
     </font>
     <font>
       <i/>
+      <sz val="8"/>
+      <color rgb="FF47484C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="8"/>
       <color rgb="FF47484C"/>
       <name val="Arial"/>
@@ -3993,7 +4543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3273017-25D8-4705-B64D-E4EEBFC32101}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28.21875" style="2" customWidth="1"/>
@@ -4007,7 +4557,7 @@
     <col min="10" max="10" width="40.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="7" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>26</v>
       </c>
@@ -4035,8 +4585,14 @@
       <c r="I1" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="J1" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>175</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" ht="154.19999999999999" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="154.19999999999999" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4062,7 +4618,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="215.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="215.4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4088,7 +4644,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="256.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="256.2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4115,7 +4671,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4144,7 +4700,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4173,7 +4729,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4205,7 +4761,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4234,7 +4790,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4263,7 +4819,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4295,7 +4851,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4324,7 +4880,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4353,12 +4909,12 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4387,7 +4943,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="360" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="360" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4416,7 +4972,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:10" s="12" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" s="12" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A16" s="12">
         <v>15</v>
       </c>
@@ -4606,7 +5162,7 @@
       <c r="D22" s="1">
         <v>45383</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="11" t="s">
         <v>153</v>
       </c>
       <c r="F22" s="2" t="s">
@@ -4649,6 +5205,168 @@
       </c>
       <c r="I23" s="2" t="s">
         <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D24" s="1">
+        <v>45078</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D25" s="1">
+        <v>44958</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="1">
+        <v>44378</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="1">
+        <v>43925</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="12" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="12">
+        <v>27</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="14">
+        <v>44470</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="197.4" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D29" s="1">
+        <v>45292</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -4670,6 +5388,13 @@
     <hyperlink ref="C20" r:id="rId15" display="https://arxiv.org/abs/2408.07004" xr:uid="{9A475C34-F3D2-4BD8-900A-086E09E58594}"/>
     <hyperlink ref="C22" r:id="rId16" display="https://ieeexplore.ieee.org/document/10447454" xr:uid="{6B4D055D-5DA2-4ADC-B931-B85BCE8326AA}"/>
     <hyperlink ref="C23" r:id="rId17" display="https://aclanthology.org/2023.emnlp-main.921/" xr:uid="{CBC3D013-B497-49AA-A3BF-10F361C07017}"/>
+    <hyperlink ref="C24" r:id="rId18" display="https://aclanthology.org/2023.inlg-main.3/" xr:uid="{2C70D679-6874-4A32-B394-DE8078918BC2}"/>
+    <hyperlink ref="B24" r:id="rId19" display="https://aclanthology.org/2023.inlg-main.3.pdf" xr:uid="{96A42630-64DF-445C-9AA6-EAF5C8EF714C}"/>
+    <hyperlink ref="C25" r:id="rId20" display="https://arxiv.org/abs/2302.00539" xr:uid="{D9A12C70-0468-4FB5-B9B9-48850E614F95}"/>
+    <hyperlink ref="C26" r:id="rId21" display="https://arxiv.org/abs/2107.01614" xr:uid="{B311B9FF-1E74-4350-BB2E-9F8452AD7C69}"/>
+    <hyperlink ref="C27" r:id="rId22" display="https://pubmed.ncbi.nlm.nih.gov/34350426/" xr:uid="{D434CFB1-40DD-4122-8E69-F7F6EA3277F0}"/>
+    <hyperlink ref="C28" r:id="rId23" display="https://arxiv.org/abs/2110.06500" xr:uid="{BEE0DB7E-EE1A-4795-ACF9-5E7286358DC8}"/>
+    <hyperlink ref="C29" r:id="rId24" display="https://www.academia.edu/124958504/Navigating_Data_Protection_Challenges_in_the_Era_of_Artificial_Intelligence_A_Comprehensive_Review" xr:uid="{40E33EEC-6A75-4617-BE2D-ED27CBBF739A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Machine Learning/PII/Interim-report/Papers/Papers-Table.xlsx
+++ b/Machine Learning/PII/Interim-report/Papers/Papers-Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\git\Machine Learning\PII\Interim-report\Papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00020E7-CFA5-4F98-92CD-5451111677E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4E3103-B6E0-424D-A661-677C7101B382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA821531-E608-40CF-B71D-4D7770E4DFA0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="208">
   <si>
     <t>Bae, Y., Kim, M., Lee, J., Kim, S., Kim, J., Choi, Y., &amp; Mireshghallah, N. (2025). Privacy-Preserving LLM Interaction with Socratic Chain-of-Thought Reasoning and Homomorphically Encrypted Vector Databases.</t>
   </si>
@@ -4089,6 +4089,32 @@
       </rPr>
       <t> like federated learning and differential privacy as promising solutions for preserving privacy in AI applications. Ultimately, the paper aims to synthesize current knowledge to provide valuable insights for policymakers, practitioners, and researchers navigating this evolving landscape.</t>
     </r>
+  </si>
+  <si>
+    <t>This paper's main focus is a comprehensive review of the intersection of Artificial Intelligence (AI) and data protection. It specifically explores challenges and opportunities arising from AI's integration into various sectors, with a particular emphasis on data protection and privacy.
+Key aspects of its focus include:
+• Examining regulatory frameworks such as the GDPR and CCPA.
+• Analyzing ethical considerations, including algorithmic bias, fairness, and accountability in AI decision-making.
+• Investigating technological innovations designed to enhance data privacy, such as federated learning and differential privacy.
+By synthesizing current literature and empirical findings, the review aims to provide insights for policymakers, practitioners, and researchers navigating AI-driven data governance complexities</t>
+  </si>
+  <si>
+    <t>The methodology employed in this paper is a systematic literature review to explore the intersection of Artificial Intelligence (AI) and data protection.
+The process involved:
+• Literature Search Strategy: Searching electronic databases such as Scopus, PubMed, IEEE Xplore, and Google Scholar using keywords like "Artificial Intelligence," "data protection," "privacy," "regulation," "ethical considerations," and "technological innovations" with Boolean operators.
+• Inclusion/Exclusion Criteria: Including English peer-reviewed journal articles, conference proceedings, and grey literature published between January 2015 and December 2023, relevant to AI's impact on data protection. Studies not directly related or lacking methodological rigor were excluded.
+• Screening and Selection: Initial screening by title and abstract, followed by detailed full-text examination and removal of duplicates.
+• Data Extraction and Synthesis: Capturing key findings and categorizing them into thematic domains like regulatory landscapes, ethical considerations, and technological advancements.
+• Quality Assessment: Prioritizing studies with robust theoretical frameworks and empirical evidence.
+• Data Analysis: Using formulas to quantify regulatory impact (e.g., GDPR studies percentage) and ethical considerations (e.g., prevalence of fairness, transparency, accountability)</t>
+  </si>
+  <si>
+    <t>This paper achieved a comprehensive understanding of AI's impact on data protection by synthesizing current literature and empirical findings. It successfully elucidated regulatory frameworks (like GDPR and CCPA), ethical considerations (such as fairness and transparency), and technological innovations (like federated learning and differential privacy).
+The review provided quantitative analysis showing a predominant focus on GDPR in regulatory studies and highlighted the prevalence of ethical principles in discussions. It also evaluated the efficacy of privacy-preserving technologies, demonstrating their potential to enhance data protection in AI applications. These insights aim to inform policymakers, practitioners, and researchers</t>
+  </si>
+  <si>
+    <t>he paper identifies limitations including potential biases in study selection and interpretation, language restrictions to English publications, and the dynamic nature of AI and data protection landscapes. The exclusion of non-English or unpublished works might have limited the scope.
+For future work, it suggests focusing on longitudinal studies to assess regulatory efficacy, promoting interdisciplinary collaborations for emerging ethical dilemmas, and advancing privacy-preserving technologies. It also emphasizes addressing algorithmic bias, cross-border data flows, and developing adaptive regulatory frameworks</t>
   </si>
 </sst>
 </file>
@@ -5352,7 +5378,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="197.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5367,6 +5393,18 @@
       </c>
       <c r="E29" s="2" t="s">
         <v>203</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/Machine Learning/PII/Interim-report/Papers/Papers-Table.xlsx
+++ b/Machine Learning/PII/Interim-report/Papers/Papers-Table.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\git\Machine Learning\PII\Interim-report\Papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B4E3103-B6E0-424D-A661-677C7101B382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FACFA10-53CF-4D9E-B65C-36175A7F2838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AA821531-E608-40CF-B71D-4D7770E4DFA0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AA821531-E608-40CF-B71D-4D7770E4DFA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="LLM Questions" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -4121,7 +4123,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4179,12 +4181,6 @@
     </font>
     <font>
       <i/>
-      <sz val="8"/>
-      <color rgb="FF47484C"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF47484C"/>
       <name val="Arial"/>
@@ -4570,20 +4566,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3273017-25D8-4705-B64D-E4EEBFC32101}">
   <dimension ref="A1:K29"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" customWidth="1"/>
     <col min="5" max="5" width="42" style="2" customWidth="1"/>
-    <col min="6" max="6" width="39.44140625" customWidth="1"/>
-    <col min="7" max="7" width="32.77734375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="33.44140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="29.33203125" customWidth="1"/>
-    <col min="10" max="10" width="40.77734375" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="10" max="10" width="40.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>26</v>
       </c>
@@ -4618,7 +4614,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="154.19999999999999" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="180.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4644,795 +4640,808 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="215.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="409.6" x14ac:dyDescent="0.25">
       <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1">
+        <v>45778</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="1">
+        <v>45748</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="1">
+        <v>45748</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="1">
+        <v>45505</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>19</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="14">
+        <v>45505</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+    </row>
+    <row r="8" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="1">
+        <v>45383</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D9" s="1">
+        <v>45352</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D10" s="1">
+        <v>45292</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="1">
+        <v>45261</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12"/>
+      <c r="D12" s="1">
+        <v>45170</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D13" s="1">
         <v>45121</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="256.2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4"/>
-      <c r="D4" s="1">
-        <v>45170</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="4" t="s">
+    <row r="14" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="14">
+        <v>45078</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>23</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" s="1">
+        <v>45078</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="12" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>6</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="10">
+        <v>45047</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16"/>
+    </row>
+    <row r="17" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>18</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17" s="1">
+        <v>45047</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>24</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="B18" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" s="1">
+        <v>44958</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" s="1">
+        <v>44743</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" s="12" customFormat="1" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="1">
+        <v>44593</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J20"/>
+      <c r="K20"/>
+    </row>
+    <row r="21" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="12">
+        <v>27</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="14">
+        <v>44470</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+    </row>
+    <row r="22" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>25</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>23</v>
+      <c r="B22" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D22" s="1">
+        <v>44378</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="1">
-        <v>45778</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>34</v>
+    <row r="23" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="1">
+        <v>44228</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A6">
+    <row r="24" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C24" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D24" s="1">
         <v>44136</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H24" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I24" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="10">
-        <v>45047</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>52</v>
+    <row r="25" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>26</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="1">
+        <v>43925</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>194</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="1">
-        <v>45505</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>59</v>
+    <row r="26" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>10</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="1">
+        <v>43922</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A9">
+    <row r="27" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C27" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D27" s="1">
         <v>43709</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F27" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A10">
+    <row r="28" spans="1:11" s="12" customFormat="1" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C28" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D28" s="10">
         <v>43435</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I28" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J28" s="2" t="s">
         <v>73</v>
       </c>
+      <c r="K28"/>
     </row>
-    <row r="11" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="1">
-        <v>43922</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" s="1">
-        <v>44228</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="1">
-        <v>44743</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="360" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" s="1">
-        <v>45748</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" s="12" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="12">
-        <v>15</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D16" s="14">
-        <v>45078</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="360" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D17" s="1">
-        <v>44593</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="1">
-        <v>45748</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="374.4" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="D19" s="1">
-        <v>45047</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="12" customFormat="1" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="12">
-        <v>19</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="D20" s="14">
-        <v>45505</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D21" s="1">
-        <v>45352</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="1">
-        <v>45383</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" s="1">
-        <v>45261</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" s="1">
-        <v>45078</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="D25" s="1">
-        <v>44958</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="D26" s="1">
-        <v>44378</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="D27" s="1">
-        <v>43925</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="12" customFormat="1" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="12">
-        <v>27</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" s="14">
-        <v>44470</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="G28" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="D29" s="1">
-        <v>45292</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>207</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{E3273017-25D8-4705-B64D-E4EEBFC32101}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K30">
+    <sortCondition descending="1" ref="D1:D30"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" display="https://papers.ssrn.com/sol3/papers.cfm?abstract_id=5259722" xr:uid="{F6709356-ED4B-4A5B-BFD4-4B669ED87300}"/>
-    <hyperlink ref="C6" r:id="rId2" display="https://aclanthology.org/2020.privatenlp-1.5/" xr:uid="{E91A3E06-C7C0-4232-9B9C-958A53660944}"/>
-    <hyperlink ref="C7" r:id="rId3" display="https://arxiv.org/abs/2305.18396" xr:uid="{89A300C5-1B74-446C-9D44-77A7BAE19972}"/>
-    <hyperlink ref="C8" r:id="rId4" display="https://arxiv.org/abs/2310.09130" xr:uid="{D265B287-0711-4975-B3DA-D46D676E79F2}"/>
-    <hyperlink ref="C9" r:id="rId5" display="https://arxiv.org/abs/1909.09145" xr:uid="{E6F068DA-77A1-4AF2-BCB8-BAB1BC5F99D5}"/>
-    <hyperlink ref="C10" r:id="rId6" display="https://arxiv.org/abs/1812.00564" xr:uid="{991C14EA-F987-461D-BB97-BBF6D1AC7EB3}"/>
-    <hyperlink ref="C11" r:id="rId7" display="https://ieeexplore.ieee.org/document/9069945" xr:uid="{9383D204-9E86-40EF-B6EF-4CF1D0575D5D}"/>
-    <hyperlink ref="C12" r:id="rId8" display="https://arxiv.org/abs/2102.08504" xr:uid="{237D23DB-0320-4B06-979D-E8C5F5641137}"/>
-    <hyperlink ref="C14" r:id="rId9" display="https://arxiv.org/abs/2110.06500" xr:uid="{593B325C-8AB0-44E3-B5C4-EBAD0E85E02F}"/>
-    <hyperlink ref="C15" r:id="rId10" display="https://dl.acm.org/doi/abs/10.1145/3696410.3714531" xr:uid="{D2AD492D-EBD8-437E-B49F-4D74653F8A2E}"/>
-    <hyperlink ref="C16" r:id="rId11" display="https://arxiv.org/abs/2306.08223" xr:uid="{A7C8098E-424D-4A84-A80E-7643C924F821}"/>
-    <hyperlink ref="C17" r:id="rId12" display="https://arxiv.org/abs/2202.05520" xr:uid="{2AFA1272-530E-472C-AA98-4FAB1E668DD0}"/>
-    <hyperlink ref="C18" r:id="rId13" display="https://dl.acm.org/doi/full/10.1145/3706598.3713701" xr:uid="{FA079AEC-4E31-444F-B03C-FEF634B1EBC1}"/>
-    <hyperlink ref="C19" r:id="rId14" display="https://arxiv.org/abs/2305.15008" xr:uid="{2E5787C8-6AA0-4059-8C31-659EF5D13331}"/>
-    <hyperlink ref="C20" r:id="rId15" display="https://arxiv.org/abs/2408.07004" xr:uid="{9A475C34-F3D2-4BD8-900A-086E09E58594}"/>
-    <hyperlink ref="C22" r:id="rId16" display="https://ieeexplore.ieee.org/document/10447454" xr:uid="{6B4D055D-5DA2-4ADC-B931-B85BCE8326AA}"/>
-    <hyperlink ref="C23" r:id="rId17" display="https://aclanthology.org/2023.emnlp-main.921/" xr:uid="{CBC3D013-B497-49AA-A3BF-10F361C07017}"/>
-    <hyperlink ref="C24" r:id="rId18" display="https://aclanthology.org/2023.inlg-main.3/" xr:uid="{2C70D679-6874-4A32-B394-DE8078918BC2}"/>
-    <hyperlink ref="B24" r:id="rId19" display="https://aclanthology.org/2023.inlg-main.3.pdf" xr:uid="{96A42630-64DF-445C-9AA6-EAF5C8EF714C}"/>
-    <hyperlink ref="C25" r:id="rId20" display="https://arxiv.org/abs/2302.00539" xr:uid="{D9A12C70-0468-4FB5-B9B9-48850E614F95}"/>
-    <hyperlink ref="C26" r:id="rId21" display="https://arxiv.org/abs/2107.01614" xr:uid="{B311B9FF-1E74-4350-BB2E-9F8452AD7C69}"/>
-    <hyperlink ref="C27" r:id="rId22" display="https://pubmed.ncbi.nlm.nih.gov/34350426/" xr:uid="{D434CFB1-40DD-4122-8E69-F7F6EA3277F0}"/>
-    <hyperlink ref="C28" r:id="rId23" display="https://arxiv.org/abs/2110.06500" xr:uid="{BEE0DB7E-EE1A-4795-ACF9-5E7286358DC8}"/>
-    <hyperlink ref="C29" r:id="rId24" display="https://www.academia.edu/124958504/Navigating_Data_Protection_Challenges_in_the_Era_of_Artificial_Intelligence_A_Comprehensive_Review" xr:uid="{40E33EEC-6A75-4617-BE2D-ED27CBBF739A}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://papers.ssrn.com/sol3/papers.cfm?abstract_id=5259722" xr:uid="{F6709356-ED4B-4A5B-BFD4-4B669ED87300}"/>
+    <hyperlink ref="C24" r:id="rId2" display="https://aclanthology.org/2020.privatenlp-1.5/" xr:uid="{E91A3E06-C7C0-4232-9B9C-958A53660944}"/>
+    <hyperlink ref="C16" r:id="rId3" display="https://arxiv.org/abs/2305.18396" xr:uid="{89A300C5-1B74-446C-9D44-77A7BAE19972}"/>
+    <hyperlink ref="C6" r:id="rId4" display="https://arxiv.org/abs/2310.09130" xr:uid="{D265B287-0711-4975-B3DA-D46D676E79F2}"/>
+    <hyperlink ref="C27" r:id="rId5" display="https://arxiv.org/abs/1909.09145" xr:uid="{E6F068DA-77A1-4AF2-BCB8-BAB1BC5F99D5}"/>
+    <hyperlink ref="C28" r:id="rId6" display="https://arxiv.org/abs/1812.00564" xr:uid="{991C14EA-F987-461D-BB97-BBF6D1AC7EB3}"/>
+    <hyperlink ref="C26" r:id="rId7" display="https://ieeexplore.ieee.org/document/9069945" xr:uid="{9383D204-9E86-40EF-B6EF-4CF1D0575D5D}"/>
+    <hyperlink ref="C23" r:id="rId8" display="https://arxiv.org/abs/2102.08504" xr:uid="{237D23DB-0320-4B06-979D-E8C5F5641137}"/>
+    <hyperlink ref="C19" r:id="rId9" display="https://arxiv.org/abs/2110.06500" xr:uid="{593B325C-8AB0-44E3-B5C4-EBAD0E85E02F}"/>
+    <hyperlink ref="C4" r:id="rId10" display="https://dl.acm.org/doi/abs/10.1145/3696410.3714531" xr:uid="{D2AD492D-EBD8-437E-B49F-4D74653F8A2E}"/>
+    <hyperlink ref="C14" r:id="rId11" display="https://arxiv.org/abs/2306.08223" xr:uid="{A7C8098E-424D-4A84-A80E-7643C924F821}"/>
+    <hyperlink ref="C20" r:id="rId12" display="https://arxiv.org/abs/2202.05520" xr:uid="{2AFA1272-530E-472C-AA98-4FAB1E668DD0}"/>
+    <hyperlink ref="C5" r:id="rId13" display="https://dl.acm.org/doi/full/10.1145/3706598.3713701" xr:uid="{FA079AEC-4E31-444F-B03C-FEF634B1EBC1}"/>
+    <hyperlink ref="C17" r:id="rId14" display="https://arxiv.org/abs/2305.15008" xr:uid="{2E5787C8-6AA0-4059-8C31-659EF5D13331}"/>
+    <hyperlink ref="C7" r:id="rId15" display="https://arxiv.org/abs/2408.07004" xr:uid="{9A475C34-F3D2-4BD8-900A-086E09E58594}"/>
+    <hyperlink ref="C8" r:id="rId16" display="https://ieeexplore.ieee.org/document/10447454" xr:uid="{6B4D055D-5DA2-4ADC-B931-B85BCE8326AA}"/>
+    <hyperlink ref="C11" r:id="rId17" display="https://aclanthology.org/2023.emnlp-main.921/" xr:uid="{CBC3D013-B497-49AA-A3BF-10F361C07017}"/>
+    <hyperlink ref="C15" r:id="rId18" display="https://aclanthology.org/2023.inlg-main.3/" xr:uid="{2C70D679-6874-4A32-B394-DE8078918BC2}"/>
+    <hyperlink ref="B15" r:id="rId19" display="https://aclanthology.org/2023.inlg-main.3.pdf" xr:uid="{96A42630-64DF-445C-9AA6-EAF5C8EF714C}"/>
+    <hyperlink ref="C18" r:id="rId20" display="https://arxiv.org/abs/2302.00539" xr:uid="{D9A12C70-0468-4FB5-B9B9-48850E614F95}"/>
+    <hyperlink ref="C22" r:id="rId21" display="https://arxiv.org/abs/2107.01614" xr:uid="{B311B9FF-1E74-4350-BB2E-9F8452AD7C69}"/>
+    <hyperlink ref="C25" r:id="rId22" display="https://pubmed.ncbi.nlm.nih.gov/34350426/" xr:uid="{D434CFB1-40DD-4122-8E69-F7F6EA3277F0}"/>
+    <hyperlink ref="C21" r:id="rId23" display="https://arxiv.org/abs/2110.06500" xr:uid="{BEE0DB7E-EE1A-4795-ACF9-5E7286358DC8}"/>
+    <hyperlink ref="C10" r:id="rId24" display="https://www.academia.edu/124958504/Navigating_Data_Protection_Challenges_in_the_Era_of_Artificial_Intelligence_A_Comprehensive_Review" xr:uid="{40E33EEC-6A75-4617-BE2D-ED27CBBF739A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5441,42 +5450,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B8FDB45-EE13-4E63-A03A-A7B6283EA313}">
   <dimension ref="B1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="78.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="78.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>113</v>
       </c>
